--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{542965EA-A45D-4D49-880B-D3E8A6D3839F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD65790-4131-4EE8-8A8B-C5426184B157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -26013,8 +26013,8 @@
         <v>1</v>
       </c>
       <c r="AB15">
-        <f>AE15*2.5</f>
-        <v>82.699999999999989</v>
+        <f>AE15*1.25</f>
+        <v>41.349999999999994</v>
       </c>
       <c r="AC15">
         <v>3</v>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A207222-D4E6-4EC6-A216-6D252F842919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79974DAD-5705-4787-8A58-791748E4A284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662745F8-5075-4D8C-A4B3-1A77A1E42C53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3A546E-F186-487D-834C-BB03EB4642B3}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79974DAD-5705-4787-8A58-791748E4A284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A484582F-E3FB-4B2B-9AAC-D6B36B447EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3A546E-F186-487D-834C-BB03EB4642B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2ACE909-89A4-4AA9-BE3E-49EFF8CC7E12}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A484582F-E3FB-4B2B-9AAC-D6B36B447EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08F9CA39-86CC-4DD9-9B1B-E419C1C0D560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2ACE909-89A4-4AA9-BE3E-49EFF8CC7E12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF6BCF0-B65E-407F-9FD0-30ACD10E3941}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08F9CA39-86CC-4DD9-9B1B-E419C1C0D560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0602484-88CC-4F00-8617-2225A43E1AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF6BCF0-B65E-407F-9FD0-30ACD10E3941}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3612A5-5A8D-4677-B25F-593F983D4F33}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0602484-88CC-4F00-8617-2225A43E1AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{470D42FC-E9A3-4173-A47A-79FA72C19F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3612A5-5A8D-4677-B25F-593F983D4F33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA867F0E-AA9F-41E1-807C-392779D29630}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{470D42FC-E9A3-4173-A47A-79FA72C19F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E494D7E-C144-4D0C-B5A6-A93F4D163008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA867F0E-AA9F-41E1-807C-392779D29630}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2E2F2A0-701A-494A-93DA-1349F69F6ACC}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E494D7E-C144-4D0C-B5A6-A93F4D163008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3742A1AF-6684-4352-844D-49085AB0A9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2E2F2A0-701A-494A-93DA-1349F69F6ACC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A421CEC5-F6E0-41E6-93AF-C9F17B3EC8C0}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3742A1AF-6684-4352-844D-49085AB0A9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A696010C-C9E6-4C78-8BCB-5A42BB879AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A421CEC5-F6E0-41E6-93AF-C9F17B3EC8C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35C20041-3CFC-4A43-AF99-37B786DB8D0A}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A696010C-C9E6-4C78-8BCB-5A42BB879AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE2FB192-06C2-485A-B07E-482008879F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35C20041-3CFC-4A43-AF99-37B786DB8D0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69460F35-E104-44C7-8D18-34DFFEE7C2AA}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE2FB192-06C2-485A-B07E-482008879F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F9F827B-8614-414D-8F4F-4F012642C7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69460F35-E104-44C7-8D18-34DFFEE7C2AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E1785B4-CE81-4B11-B2CC-2833A8D7BAA7}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F9F827B-8614-414D-8F4F-4F012642C7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9125F2DF-96C4-4620-A96A-26B62C3931C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E1785B4-CE81-4B11-B2CC-2833A8D7BAA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6736659-6D62-443A-A7C5-C47EB4A65824}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9125F2DF-96C4-4620-A96A-26B62C3931C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EFEB4C7-B5A6-494E-8867-B721771E5C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6736659-6D62-443A-A7C5-C47EB4A65824}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EFA1559-3581-4927-ACFB-96A30EE6B163}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EFEB4C7-B5A6-494E-8867-B721771E5C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C064AA5-22B3-46E7-90A3-48CF7C3B18C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EFA1559-3581-4927-ACFB-96A30EE6B163}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD781976-E75A-41D3-AEA8-432919E0695D}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C064AA5-22B3-46E7-90A3-48CF7C3B18C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB5946E8-D776-4E61-A8D1-359A52B6FFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD781976-E75A-41D3-AEA8-432919E0695D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBE7B69-F72C-47D9-BE9D-0E7CE8AA51C4}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB5946E8-D776-4E61-A8D1-359A52B6FFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2A8E310-FEAB-44BF-B259-11C9945DABBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBE7B69-F72C-47D9-BE9D-0E7CE8AA51C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3747BA05-19F8-4CD9-A17B-D37844A482D6}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB6BE51E-6BA2-4353-8583-DF88C5D54705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BAF5596-3B5A-4924-8447-66F074E2BB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5211,7 +5211,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7033E980-5E04-43A5-BB93-3713C3E7523C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AFE4892-AFBD-468C-97FB-36E90D93258E}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BAF5596-3B5A-4924-8447-66F074E2BB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE4638CD-5C2E-4BBB-A89A-BD64A836A69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5211,7 +5211,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AFE4892-AFBD-468C-97FB-36E90D93258E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A59062-5321-4E46-8AAA-D0DC52CE5832}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE4638CD-5C2E-4BBB-A89A-BD64A836A69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E700F3A8-EF12-4E80-AB70-34313CE0DB91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5211,7 +5211,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A59062-5321-4E46-8AAA-D0DC52CE5832}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1670839-A96F-4576-AADC-1C1258A55AA5}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E700F3A8-EF12-4E80-AB70-34313CE0DB91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA63C3DC-777F-48EB-B7B3-C3E6083FF511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5211,7 +5211,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1670839-A96F-4576-AADC-1C1258A55AA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE9C115-3BD7-4D41-B5E2-A9D70D2AB3C1}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA63C3DC-777F-48EB-B7B3-C3E6083FF511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86153377-5B6B-4E85-9CBF-71CAC98B1500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5211,7 +5211,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE9C115-3BD7-4D41-B5E2-A9D70D2AB3C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2294CB3C-26D5-464D-8F6C-02B355D97B0D}">
   <dimension ref="B2:AE927"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86153377-5B6B-4E85-9CBF-71CAC98B1500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25EA0612-4337-4389-A895-FF34B9C1894B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6455" uniqueCount="1534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6503" uniqueCount="1550">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2523,6 +2523,45 @@
     <t>Steam Coal - ULTRASUPERCRITICAL_w315461259-500</t>
   </si>
   <si>
+    <t>Bioenergy + CCUS_w187988970-500</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w187988970-500</t>
+  </si>
+  <si>
+    <t>CCGT_w187988970-500</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w187988970-500</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w187988970-500</t>
+  </si>
+  <si>
+    <t>Gas turbine_w187988970-500</t>
+  </si>
+  <si>
+    <t>IGCC_w187988970-500</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w187988970-500</t>
+  </si>
+  <si>
+    <t>Nuclear large_w187988970-500</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w187988970-500</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w187988970-500</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w187988970-500</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w187988970-500</t>
+  </si>
+  <si>
     <t>Bioenergy + CCUS_JP110-500</t>
   </si>
   <si>
@@ -2688,45 +2727,6 @@
     <t>Steam Coal - ULTRASUPERCRITICAL_w169359724-500</t>
   </si>
   <si>
-    <t>Bioenergy + CCUS_w187988970-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w187988970-500</t>
-  </si>
-  <si>
-    <t>CCGT_w187988970-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w187988970-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w187988970-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w187988970-500</t>
-  </si>
-  <si>
-    <t>IGCC_w187988970-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w187988970-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w187988970-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w187988970-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w187988970-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w187988970-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w187988970-500</t>
-  </si>
-  <si>
     <t>Bioenergy + CCUS_w216778426-500</t>
   </si>
   <si>
@@ -4263,12 +4263,27 @@
     <t>EN_STG4hbNREL_w151379730-500</t>
   </si>
   <si>
+    <t>EN_STG8hbNREL_w505170104-500</t>
+  </si>
+  <si>
+    <t>e_w505170104-500</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w505170104-500</t>
+  </si>
+  <si>
     <t>EN_STG8hbNREL_w179863079-275</t>
   </si>
   <si>
     <t>EN_STG4hbNREL_w179863079-275</t>
   </si>
   <si>
+    <t>EN_STG8hbNREL_w105298089-500</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w105298089-500</t>
+  </si>
+  <si>
     <t>EN_STG8hbNREL_JP5-275</t>
   </si>
   <si>
@@ -4278,12 +4293,6 @@
     <t>EN_STG4hbNREL_JP5-275</t>
   </si>
   <si>
-    <t>EN_STG8hbNREL_w105298089-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w105298089-500</t>
-  </si>
-  <si>
     <t>EN_STG8hbNREL_w150065045-500</t>
   </si>
   <si>
@@ -4326,6 +4335,12 @@
     <t>EN_STG4hbNREL_w307942220-500</t>
   </si>
   <si>
+    <t>EN_STG8hbNREL_w291678103-500</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w291678103-500</t>
+  </si>
+  <si>
     <t>EN_STG8hbNREL_w216502300-500</t>
   </si>
   <si>
@@ -4452,6 +4467,57 @@
     <t>EN_STG4hbNREL_w170974371-500</t>
   </si>
   <si>
+    <t>EN_STG8hbNREL_w659138214-500</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w659138214-500</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w801582512-275</t>
+  </si>
+  <si>
+    <t>e_w801582512-275</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w801582512-275</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w1030329139-500</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w1030329139-500</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w169031998-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w169031998-500</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_JP1-275</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_JP1-275</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w172601929-500</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w172601929-500</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_w714627759-500</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w714627759-500</t>
+  </si>
+  <si>
     <t>EN_STG8hbNREL_JP218-500</t>
   </si>
   <si>
@@ -4461,12 +4527,6 @@
     <t>EN_STG4hbNREL_JP218-500</t>
   </si>
   <si>
-    <t>EN_STG8hbNREL_w1030329139-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w1030329139-500</t>
-  </si>
-  <si>
     <t>EN_STG8hbNREL_w161870227-500</t>
   </si>
   <si>
@@ -4509,12 +4569,6 @@
     <t>EN_STG4hbNREL_w216953915-500</t>
   </si>
   <si>
-    <t>EN_STG8hbNREL_w659138214-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w659138214-500</t>
-  </si>
-  <si>
     <t>EN_STG8hbNREL_w459476442-500</t>
   </si>
   <si>
@@ -4561,12 +4615,6 @@
   </si>
   <si>
     <t>EN_STG4hbNREL_w169249243-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_JP1-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_JP1-275</t>
   </si>
   <si>
     <t>EN_STG8hbNREL_w161946849-500</t>
@@ -5211,8 +5259,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2294CB3C-26D5-464D-8F6C-02B355D97B0D}">
-  <dimension ref="B2:AE927"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12DCFD3-F3B3-4479-99A4-A4BD0525DE36}">
+  <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:31" x14ac:dyDescent="0.45">
@@ -5335,16 +5383,16 @@
         <v>316</v>
       </c>
       <c r="AB4" t="s">
-        <v>1528</v>
+        <v>1544</v>
       </c>
       <c r="AC4" t="s">
-        <v>1530</v>
+        <v>1546</v>
       </c>
       <c r="AD4" t="s">
-        <v>1531</v>
+        <v>1547</v>
       </c>
       <c r="AE4" t="s">
-        <v>1532</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="5" spans="2:31" x14ac:dyDescent="0.45">
@@ -5397,10 +5445,10 @@
         <v>527</v>
       </c>
       <c r="AA5" t="s">
-        <v>1527</v>
+        <v>1543</v>
       </c>
       <c r="AB5" t="s">
-        <v>1529</v>
+        <v>1545</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -5409,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>1533</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.45">
@@ -15416,7 +15464,7 @@
         <v>799</v>
       </c>
       <c r="W264" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X264" t="s">
         <v>527</v>
@@ -15427,10 +15475,10 @@
         <v>93</v>
       </c>
       <c r="V265" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="W265" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X265" t="s">
         <v>527</v>
@@ -15441,10 +15489,10 @@
         <v>93</v>
       </c>
       <c r="V266" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="W266" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X266" t="s">
         <v>527</v>
@@ -15455,10 +15503,10 @@
         <v>93</v>
       </c>
       <c r="V267" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="W267" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X267" t="s">
         <v>527</v>
@@ -15469,10 +15517,10 @@
         <v>93</v>
       </c>
       <c r="V268" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="W268" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X268" t="s">
         <v>527</v>
@@ -15483,10 +15531,10 @@
         <v>93</v>
       </c>
       <c r="V269" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="W269" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X269" t="s">
         <v>527</v>
@@ -15497,10 +15545,10 @@
         <v>93</v>
       </c>
       <c r="V270" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="W270" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X270" t="s">
         <v>527</v>
@@ -15511,10 +15559,10 @@
         <v>93</v>
       </c>
       <c r="V271" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="W271" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X271" t="s">
         <v>527</v>
@@ -15525,10 +15573,10 @@
         <v>93</v>
       </c>
       <c r="V272" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W272" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X272" t="s">
         <v>527</v>
@@ -15539,10 +15587,10 @@
         <v>93</v>
       </c>
       <c r="V273" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="W273" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X273" t="s">
         <v>527</v>
@@ -15553,10 +15601,10 @@
         <v>93</v>
       </c>
       <c r="V274" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="W274" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X274" t="s">
         <v>527</v>
@@ -15567,10 +15615,10 @@
         <v>93</v>
       </c>
       <c r="V275" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="W275" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X275" t="s">
         <v>527</v>
@@ -15581,10 +15629,10 @@
         <v>93</v>
       </c>
       <c r="V276" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="W276" t="s">
-        <v>800</v>
+        <v>508</v>
       </c>
       <c r="X276" t="s">
         <v>527</v>
@@ -15595,10 +15643,10 @@
         <v>93</v>
       </c>
       <c r="V277" t="s">
+        <v>812</v>
+      </c>
+      <c r="W277" t="s">
         <v>813</v>
-      </c>
-      <c r="W277" t="s">
-        <v>814</v>
       </c>
       <c r="X277" t="s">
         <v>527</v>
@@ -15609,10 +15657,10 @@
         <v>93</v>
       </c>
       <c r="V278" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="W278" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X278" t="s">
         <v>527</v>
@@ -15623,10 +15671,10 @@
         <v>93</v>
       </c>
       <c r="V279" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="W279" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X279" t="s">
         <v>527</v>
@@ -15637,10 +15685,10 @@
         <v>93</v>
       </c>
       <c r="V280" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="W280" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X280" t="s">
         <v>527</v>
@@ -15651,10 +15699,10 @@
         <v>93</v>
       </c>
       <c r="V281" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="W281" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X281" t="s">
         <v>527</v>
@@ -15665,10 +15713,10 @@
         <v>93</v>
       </c>
       <c r="V282" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="W282" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X282" t="s">
         <v>527</v>
@@ -15679,10 +15727,10 @@
         <v>93</v>
       </c>
       <c r="V283" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="W283" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X283" t="s">
         <v>527</v>
@@ -15693,10 +15741,10 @@
         <v>93</v>
       </c>
       <c r="V284" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="W284" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X284" t="s">
         <v>527</v>
@@ -15707,10 +15755,10 @@
         <v>93</v>
       </c>
       <c r="V285" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="W285" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X285" t="s">
         <v>527</v>
@@ -15721,10 +15769,10 @@
         <v>93</v>
       </c>
       <c r="V286" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="W286" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X286" t="s">
         <v>527</v>
@@ -15735,10 +15783,10 @@
         <v>93</v>
       </c>
       <c r="V287" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="W287" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X287" t="s">
         <v>527</v>
@@ -15749,10 +15797,10 @@
         <v>93</v>
       </c>
       <c r="V288" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="W288" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X288" t="s">
         <v>527</v>
@@ -15763,10 +15811,10 @@
         <v>93</v>
       </c>
       <c r="V289" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="W289" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="X289" t="s">
         <v>527</v>
@@ -15777,10 +15825,10 @@
         <v>93</v>
       </c>
       <c r="V290" t="s">
+        <v>826</v>
+      </c>
+      <c r="W290" t="s">
         <v>827</v>
-      </c>
-      <c r="W290" t="s">
-        <v>828</v>
       </c>
       <c r="X290" t="s">
         <v>527</v>
@@ -15791,10 +15839,10 @@
         <v>93</v>
       </c>
       <c r="V291" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="W291" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X291" t="s">
         <v>527</v>
@@ -15805,10 +15853,10 @@
         <v>93</v>
       </c>
       <c r="V292" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="W292" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X292" t="s">
         <v>527</v>
@@ -15819,10 +15867,10 @@
         <v>93</v>
       </c>
       <c r="V293" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="W293" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X293" t="s">
         <v>527</v>
@@ -15833,10 +15881,10 @@
         <v>93</v>
       </c>
       <c r="V294" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="W294" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X294" t="s">
         <v>527</v>
@@ -15847,10 +15895,10 @@
         <v>93</v>
       </c>
       <c r="V295" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="W295" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X295" t="s">
         <v>527</v>
@@ -15861,10 +15909,10 @@
         <v>93</v>
       </c>
       <c r="V296" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="W296" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X296" t="s">
         <v>527</v>
@@ -15875,10 +15923,10 @@
         <v>93</v>
       </c>
       <c r="V297" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="W297" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X297" t="s">
         <v>527</v>
@@ -15889,10 +15937,10 @@
         <v>93</v>
       </c>
       <c r="V298" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="W298" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X298" t="s">
         <v>527</v>
@@ -15903,10 +15951,10 @@
         <v>93</v>
       </c>
       <c r="V299" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="W299" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X299" t="s">
         <v>527</v>
@@ -15917,10 +15965,10 @@
         <v>93</v>
       </c>
       <c r="V300" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="W300" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X300" t="s">
         <v>527</v>
@@ -15931,10 +15979,10 @@
         <v>93</v>
       </c>
       <c r="V301" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="W301" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X301" t="s">
         <v>527</v>
@@ -15945,10 +15993,10 @@
         <v>93</v>
       </c>
       <c r="V302" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W302" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="X302" t="s">
         <v>527</v>
@@ -15959,10 +16007,10 @@
         <v>93</v>
       </c>
       <c r="V303" t="s">
+        <v>840</v>
+      </c>
+      <c r="W303" t="s">
         <v>841</v>
-      </c>
-      <c r="W303" t="s">
-        <v>501</v>
       </c>
       <c r="X303" t="s">
         <v>527</v>
@@ -15976,7 +16024,7 @@
         <v>842</v>
       </c>
       <c r="W304" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X304" t="s">
         <v>527</v>
@@ -15990,7 +16038,7 @@
         <v>843</v>
       </c>
       <c r="W305" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X305" t="s">
         <v>527</v>
@@ -16004,7 +16052,7 @@
         <v>844</v>
       </c>
       <c r="W306" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X306" t="s">
         <v>527</v>
@@ -16018,7 +16066,7 @@
         <v>845</v>
       </c>
       <c r="W307" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X307" t="s">
         <v>527</v>
@@ -16032,7 +16080,7 @@
         <v>846</v>
       </c>
       <c r="W308" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X308" t="s">
         <v>527</v>
@@ -16046,7 +16094,7 @@
         <v>847</v>
       </c>
       <c r="W309" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X309" t="s">
         <v>527</v>
@@ -16060,7 +16108,7 @@
         <v>848</v>
       </c>
       <c r="W310" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X310" t="s">
         <v>527</v>
@@ -16074,7 +16122,7 @@
         <v>849</v>
       </c>
       <c r="W311" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X311" t="s">
         <v>527</v>
@@ -16088,7 +16136,7 @@
         <v>850</v>
       </c>
       <c r="W312" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X312" t="s">
         <v>527</v>
@@ -16102,7 +16150,7 @@
         <v>851</v>
       </c>
       <c r="W313" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X313" t="s">
         <v>527</v>
@@ -16116,7 +16164,7 @@
         <v>852</v>
       </c>
       <c r="W314" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X314" t="s">
         <v>527</v>
@@ -16130,7 +16178,7 @@
         <v>853</v>
       </c>
       <c r="W315" t="s">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="X315" t="s">
         <v>527</v>
@@ -16144,7 +16192,7 @@
         <v>854</v>
       </c>
       <c r="W316" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X316" t="s">
         <v>527</v>
@@ -16158,7 +16206,7 @@
         <v>855</v>
       </c>
       <c r="W317" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X317" t="s">
         <v>527</v>
@@ -16172,7 +16220,7 @@
         <v>856</v>
       </c>
       <c r="W318" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X318" t="s">
         <v>527</v>
@@ -16186,7 +16234,7 @@
         <v>857</v>
       </c>
       <c r="W319" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X319" t="s">
         <v>527</v>
@@ -16200,7 +16248,7 @@
         <v>858</v>
       </c>
       <c r="W320" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X320" t="s">
         <v>527</v>
@@ -16214,7 +16262,7 @@
         <v>859</v>
       </c>
       <c r="W321" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X321" t="s">
         <v>527</v>
@@ -16228,7 +16276,7 @@
         <v>860</v>
       </c>
       <c r="W322" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X322" t="s">
         <v>527</v>
@@ -16242,7 +16290,7 @@
         <v>861</v>
       </c>
       <c r="W323" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X323" t="s">
         <v>527</v>
@@ -16256,7 +16304,7 @@
         <v>862</v>
       </c>
       <c r="W324" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X324" t="s">
         <v>527</v>
@@ -16270,7 +16318,7 @@
         <v>863</v>
       </c>
       <c r="W325" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X325" t="s">
         <v>527</v>
@@ -16284,7 +16332,7 @@
         <v>864</v>
       </c>
       <c r="W326" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X326" t="s">
         <v>527</v>
@@ -16298,7 +16346,7 @@
         <v>865</v>
       </c>
       <c r="W327" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X327" t="s">
         <v>527</v>
@@ -16312,7 +16360,7 @@
         <v>866</v>
       </c>
       <c r="W328" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="X328" t="s">
         <v>527</v>
@@ -22724,7 +22772,7 @@
         <v>1379</v>
       </c>
       <c r="W786" t="s">
-        <v>828</v>
+        <v>1380</v>
       </c>
       <c r="X786" t="s">
         <v>527</v>
@@ -22735,10 +22783,10 @@
         <v>93</v>
       </c>
       <c r="V787" t="s">
+        <v>1381</v>
+      </c>
+      <c r="W787" t="s">
         <v>1380</v>
-      </c>
-      <c r="W787" t="s">
-        <v>828</v>
       </c>
       <c r="X787" t="s">
         <v>527</v>
@@ -22749,10 +22797,10 @@
         <v>93</v>
       </c>
       <c r="V788" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="W788" t="s">
-        <v>1382</v>
+        <v>841</v>
       </c>
       <c r="X788" t="s">
         <v>527</v>
@@ -22766,7 +22814,7 @@
         <v>1383</v>
       </c>
       <c r="W789" t="s">
-        <v>1382</v>
+        <v>841</v>
       </c>
       <c r="X789" t="s">
         <v>527</v>
@@ -22808,7 +22856,7 @@
         <v>1386</v>
       </c>
       <c r="W792" t="s">
-        <v>492</v>
+        <v>1387</v>
       </c>
       <c r="X792" t="s">
         <v>527</v>
@@ -22819,10 +22867,10 @@
         <v>93</v>
       </c>
       <c r="V793" t="s">
+        <v>1388</v>
+      </c>
+      <c r="W793" t="s">
         <v>1387</v>
-      </c>
-      <c r="W793" t="s">
-        <v>492</v>
       </c>
       <c r="X793" t="s">
         <v>527</v>
@@ -22833,10 +22881,10 @@
         <v>93</v>
       </c>
       <c r="V794" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="W794" t="s">
-        <v>1389</v>
+        <v>492</v>
       </c>
       <c r="X794" t="s">
         <v>527</v>
@@ -22850,7 +22898,7 @@
         <v>1390</v>
       </c>
       <c r="W795" t="s">
-        <v>1389</v>
+        <v>492</v>
       </c>
       <c r="X795" t="s">
         <v>527</v>
@@ -22864,7 +22912,7 @@
         <v>1391</v>
       </c>
       <c r="W796" t="s">
-        <v>1131</v>
+        <v>1392</v>
       </c>
       <c r="X796" t="s">
         <v>527</v>
@@ -22875,10 +22923,10 @@
         <v>93</v>
       </c>
       <c r="V797" t="s">
+        <v>1393</v>
+      </c>
+      <c r="W797" t="s">
         <v>1392</v>
-      </c>
-      <c r="W797" t="s">
-        <v>1131</v>
       </c>
       <c r="X797" t="s">
         <v>527</v>
@@ -22889,10 +22937,10 @@
         <v>93</v>
       </c>
       <c r="V798" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="W798" t="s">
-        <v>515</v>
+        <v>1131</v>
       </c>
       <c r="X798" t="s">
         <v>527</v>
@@ -22903,10 +22951,10 @@
         <v>93</v>
       </c>
       <c r="V799" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="W799" t="s">
-        <v>515</v>
+        <v>1131</v>
       </c>
       <c r="X799" t="s">
         <v>527</v>
@@ -22917,10 +22965,10 @@
         <v>93</v>
       </c>
       <c r="V800" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="W800" t="s">
-        <v>734</v>
+        <v>515</v>
       </c>
       <c r="X800" t="s">
         <v>527</v>
@@ -22931,10 +22979,10 @@
         <v>93</v>
       </c>
       <c r="V801" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="W801" t="s">
-        <v>734</v>
+        <v>515</v>
       </c>
       <c r="X801" t="s">
         <v>527</v>
@@ -22945,10 +22993,10 @@
         <v>93</v>
       </c>
       <c r="V802" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="W802" t="s">
-        <v>1398</v>
+        <v>734</v>
       </c>
       <c r="X802" t="s">
         <v>527</v>
@@ -22962,7 +23010,7 @@
         <v>1399</v>
       </c>
       <c r="W803" t="s">
-        <v>1398</v>
+        <v>734</v>
       </c>
       <c r="X803" t="s">
         <v>527</v>
@@ -22976,7 +23024,7 @@
         <v>1400</v>
       </c>
       <c r="W804" t="s">
-        <v>511</v>
+        <v>1401</v>
       </c>
       <c r="X804" t="s">
         <v>527</v>
@@ -22987,10 +23035,10 @@
         <v>93</v>
       </c>
       <c r="V805" t="s">
+        <v>1402</v>
+      </c>
+      <c r="W805" t="s">
         <v>1401</v>
-      </c>
-      <c r="W805" t="s">
-        <v>511</v>
       </c>
       <c r="X805" t="s">
         <v>527</v>
@@ -23001,10 +23049,10 @@
         <v>93</v>
       </c>
       <c r="V806" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="W806" t="s">
-        <v>1403</v>
+        <v>512</v>
       </c>
       <c r="X806" t="s">
         <v>527</v>
@@ -23018,7 +23066,7 @@
         <v>1404</v>
       </c>
       <c r="W807" t="s">
-        <v>1403</v>
+        <v>512</v>
       </c>
       <c r="X807" t="s">
         <v>527</v>
@@ -23032,7 +23080,7 @@
         <v>1405</v>
       </c>
       <c r="W808" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="X808" t="s">
         <v>527</v>
@@ -23046,7 +23094,7 @@
         <v>1406</v>
       </c>
       <c r="W809" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="X809" t="s">
         <v>527</v>
@@ -23060,7 +23108,7 @@
         <v>1407</v>
       </c>
       <c r="W810" t="s">
-        <v>513</v>
+        <v>1408</v>
       </c>
       <c r="X810" t="s">
         <v>527</v>
@@ -23071,10 +23119,10 @@
         <v>93</v>
       </c>
       <c r="V811" t="s">
+        <v>1409</v>
+      </c>
+      <c r="W811" t="s">
         <v>1408</v>
-      </c>
-      <c r="W811" t="s">
-        <v>513</v>
       </c>
       <c r="X811" t="s">
         <v>527</v>
@@ -23085,10 +23133,10 @@
         <v>93</v>
       </c>
       <c r="V812" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="W812" t="s">
-        <v>1410</v>
+        <v>503</v>
       </c>
       <c r="X812" t="s">
         <v>527</v>
@@ -23102,7 +23150,7 @@
         <v>1411</v>
       </c>
       <c r="W813" t="s">
-        <v>1410</v>
+        <v>503</v>
       </c>
       <c r="X813" t="s">
         <v>527</v>
@@ -23116,7 +23164,7 @@
         <v>1412</v>
       </c>
       <c r="W814" t="s">
-        <v>800</v>
+        <v>513</v>
       </c>
       <c r="X814" t="s">
         <v>527</v>
@@ -23130,7 +23178,7 @@
         <v>1413</v>
       </c>
       <c r="W815" t="s">
-        <v>800</v>
+        <v>513</v>
       </c>
       <c r="X815" t="s">
         <v>527</v>
@@ -23144,7 +23192,7 @@
         <v>1414</v>
       </c>
       <c r="W816" t="s">
-        <v>814</v>
+        <v>1415</v>
       </c>
       <c r="X816" t="s">
         <v>527</v>
@@ -23155,10 +23203,10 @@
         <v>93</v>
       </c>
       <c r="V817" t="s">
+        <v>1416</v>
+      </c>
+      <c r="W817" t="s">
         <v>1415</v>
-      </c>
-      <c r="W817" t="s">
-        <v>814</v>
       </c>
       <c r="X817" t="s">
         <v>527</v>
@@ -23169,10 +23217,10 @@
         <v>93</v>
       </c>
       <c r="V818" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="W818" t="s">
-        <v>923</v>
+        <v>813</v>
       </c>
       <c r="X818" t="s">
         <v>527</v>
@@ -23183,10 +23231,10 @@
         <v>93</v>
       </c>
       <c r="V819" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="W819" t="s">
-        <v>923</v>
+        <v>813</v>
       </c>
       <c r="X819" t="s">
         <v>527</v>
@@ -23197,10 +23245,10 @@
         <v>93</v>
       </c>
       <c r="V820" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="W820" t="s">
-        <v>501</v>
+        <v>827</v>
       </c>
       <c r="X820" t="s">
         <v>527</v>
@@ -23211,10 +23259,10 @@
         <v>93</v>
       </c>
       <c r="V821" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="W821" t="s">
-        <v>501</v>
+        <v>827</v>
       </c>
       <c r="X821" t="s">
         <v>527</v>
@@ -23225,10 +23273,10 @@
         <v>93</v>
       </c>
       <c r="V822" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="W822" t="s">
-        <v>868</v>
+        <v>923</v>
       </c>
       <c r="X822" t="s">
         <v>527</v>
@@ -23239,10 +23287,10 @@
         <v>93</v>
       </c>
       <c r="V823" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="W823" t="s">
-        <v>868</v>
+        <v>923</v>
       </c>
       <c r="X823" t="s">
         <v>527</v>
@@ -23253,10 +23301,10 @@
         <v>93</v>
       </c>
       <c r="V824" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="W824" t="s">
-        <v>895</v>
+        <v>501</v>
       </c>
       <c r="X824" t="s">
         <v>527</v>
@@ -23267,10 +23315,10 @@
         <v>93</v>
       </c>
       <c r="V825" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="W825" t="s">
-        <v>895</v>
+        <v>501</v>
       </c>
       <c r="X825" t="s">
         <v>527</v>
@@ -23281,10 +23329,10 @@
         <v>93</v>
       </c>
       <c r="V826" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="W826" t="s">
-        <v>909</v>
+        <v>868</v>
       </c>
       <c r="X826" t="s">
         <v>527</v>
@@ -23295,10 +23343,10 @@
         <v>93</v>
       </c>
       <c r="V827" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="W827" t="s">
-        <v>909</v>
+        <v>868</v>
       </c>
       <c r="X827" t="s">
         <v>527</v>
@@ -23309,10 +23357,10 @@
         <v>93</v>
       </c>
       <c r="V828" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="W828" t="s">
-        <v>504</v>
+        <v>895</v>
       </c>
       <c r="X828" t="s">
         <v>527</v>
@@ -23323,10 +23371,10 @@
         <v>93</v>
       </c>
       <c r="V829" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="W829" t="s">
-        <v>504</v>
+        <v>895</v>
       </c>
       <c r="X829" t="s">
         <v>527</v>
@@ -23337,10 +23385,10 @@
         <v>93</v>
       </c>
       <c r="V830" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="W830" t="s">
-        <v>978</v>
+        <v>909</v>
       </c>
       <c r="X830" t="s">
         <v>527</v>
@@ -23351,10 +23399,10 @@
         <v>93</v>
       </c>
       <c r="V831" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="W831" t="s">
-        <v>978</v>
+        <v>909</v>
       </c>
       <c r="X831" t="s">
         <v>527</v>
@@ -23365,10 +23413,10 @@
         <v>93</v>
       </c>
       <c r="V832" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="W832" t="s">
-        <v>992</v>
+        <v>504</v>
       </c>
       <c r="X832" t="s">
         <v>527</v>
@@ -23379,10 +23427,10 @@
         <v>93</v>
       </c>
       <c r="V833" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="W833" t="s">
-        <v>992</v>
+        <v>504</v>
       </c>
       <c r="X833" t="s">
         <v>527</v>
@@ -23393,10 +23441,10 @@
         <v>93</v>
       </c>
       <c r="V834" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="W834" t="s">
-        <v>1006</v>
+        <v>978</v>
       </c>
       <c r="X834" t="s">
         <v>527</v>
@@ -23407,10 +23455,10 @@
         <v>93</v>
       </c>
       <c r="V835" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="W835" t="s">
-        <v>1006</v>
+        <v>978</v>
       </c>
       <c r="X835" t="s">
         <v>527</v>
@@ -23421,10 +23469,10 @@
         <v>93</v>
       </c>
       <c r="V836" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="W836" t="s">
-        <v>507</v>
+        <v>992</v>
       </c>
       <c r="X836" t="s">
         <v>527</v>
@@ -23435,10 +23483,10 @@
         <v>93</v>
       </c>
       <c r="V837" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="W837" t="s">
-        <v>507</v>
+        <v>992</v>
       </c>
       <c r="X837" t="s">
         <v>527</v>
@@ -23449,10 +23497,10 @@
         <v>93</v>
       </c>
       <c r="V838" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="W838" t="s">
-        <v>1061</v>
+        <v>1006</v>
       </c>
       <c r="X838" t="s">
         <v>527</v>
@@ -23463,10 +23511,10 @@
         <v>93</v>
       </c>
       <c r="V839" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="W839" t="s">
-        <v>1061</v>
+        <v>1006</v>
       </c>
       <c r="X839" t="s">
         <v>527</v>
@@ -23477,10 +23525,10 @@
         <v>93</v>
       </c>
       <c r="V840" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="W840" t="s">
-        <v>1103</v>
+        <v>507</v>
       </c>
       <c r="X840" t="s">
         <v>527</v>
@@ -23491,10 +23539,10 @@
         <v>93</v>
       </c>
       <c r="V841" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="W841" t="s">
-        <v>1103</v>
+        <v>507</v>
       </c>
       <c r="X841" t="s">
         <v>527</v>
@@ -23505,10 +23553,10 @@
         <v>93</v>
       </c>
       <c r="V842" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="W842" t="s">
-        <v>1117</v>
+        <v>1061</v>
       </c>
       <c r="X842" t="s">
         <v>527</v>
@@ -23519,10 +23567,10 @@
         <v>93</v>
       </c>
       <c r="V843" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="W843" t="s">
-        <v>1117</v>
+        <v>1061</v>
       </c>
       <c r="X843" t="s">
         <v>527</v>
@@ -23533,10 +23581,10 @@
         <v>93</v>
       </c>
       <c r="V844" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="W844" t="s">
-        <v>1443</v>
+        <v>1103</v>
       </c>
       <c r="X844" t="s">
         <v>527</v>
@@ -23550,7 +23598,7 @@
         <v>1444</v>
       </c>
       <c r="W845" t="s">
-        <v>1443</v>
+        <v>1103</v>
       </c>
       <c r="X845" t="s">
         <v>527</v>
@@ -23564,7 +23612,7 @@
         <v>1445</v>
       </c>
       <c r="W846" t="s">
-        <v>1145</v>
+        <v>1117</v>
       </c>
       <c r="X846" t="s">
         <v>527</v>
@@ -23578,7 +23626,7 @@
         <v>1446</v>
       </c>
       <c r="W847" t="s">
-        <v>1145</v>
+        <v>1117</v>
       </c>
       <c r="X847" t="s">
         <v>527</v>
@@ -23592,7 +23640,7 @@
         <v>1447</v>
       </c>
       <c r="W848" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="X848" t="s">
         <v>527</v>
@@ -23606,7 +23654,7 @@
         <v>1448</v>
       </c>
       <c r="W849" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="X849" t="s">
         <v>527</v>
@@ -23620,7 +23668,7 @@
         <v>1449</v>
       </c>
       <c r="W850" t="s">
-        <v>1152</v>
+        <v>1450</v>
       </c>
       <c r="X850" t="s">
         <v>527</v>
@@ -23631,10 +23679,10 @@
         <v>93</v>
       </c>
       <c r="V851" t="s">
+        <v>1451</v>
+      </c>
+      <c r="W851" t="s">
         <v>1450</v>
-      </c>
-      <c r="W851" t="s">
-        <v>1152</v>
       </c>
       <c r="X851" t="s">
         <v>527</v>
@@ -23645,10 +23693,10 @@
         <v>93</v>
       </c>
       <c r="V852" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="W852" t="s">
-        <v>1156</v>
+        <v>1145</v>
       </c>
       <c r="X852" t="s">
         <v>527</v>
@@ -23659,10 +23707,10 @@
         <v>93</v>
       </c>
       <c r="V853" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="W853" t="s">
-        <v>1156</v>
+        <v>1145</v>
       </c>
       <c r="X853" t="s">
         <v>527</v>
@@ -23673,10 +23721,10 @@
         <v>93</v>
       </c>
       <c r="V854" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="W854" t="s">
-        <v>1160</v>
+        <v>1455</v>
       </c>
       <c r="X854" t="s">
         <v>527</v>
@@ -23687,10 +23735,10 @@
         <v>93</v>
       </c>
       <c r="V855" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="W855" t="s">
-        <v>1160</v>
+        <v>1455</v>
       </c>
       <c r="X855" t="s">
         <v>527</v>
@@ -23701,10 +23749,10 @@
         <v>93</v>
       </c>
       <c r="V856" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="W856" t="s">
-        <v>1164</v>
+        <v>1217</v>
       </c>
       <c r="X856" t="s">
         <v>527</v>
@@ -23715,10 +23763,10 @@
         <v>93</v>
       </c>
       <c r="V857" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="W857" t="s">
-        <v>1164</v>
+        <v>1217</v>
       </c>
       <c r="X857" t="s">
         <v>527</v>
@@ -23729,10 +23777,10 @@
         <v>93</v>
       </c>
       <c r="V858" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="W858" t="s">
-        <v>1168</v>
+        <v>506</v>
       </c>
       <c r="X858" t="s">
         <v>527</v>
@@ -23743,10 +23791,10 @@
         <v>93</v>
       </c>
       <c r="V859" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="W859" t="s">
-        <v>1168</v>
+        <v>506</v>
       </c>
       <c r="X859" t="s">
         <v>527</v>
@@ -23757,10 +23805,10 @@
         <v>93</v>
       </c>
       <c r="V860" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="W860" t="s">
-        <v>1172</v>
+        <v>1462</v>
       </c>
       <c r="X860" t="s">
         <v>527</v>
@@ -23771,10 +23819,10 @@
         <v>93</v>
       </c>
       <c r="V861" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="W861" t="s">
-        <v>1172</v>
+        <v>1462</v>
       </c>
       <c r="X861" t="s">
         <v>527</v>
@@ -23785,10 +23833,10 @@
         <v>93</v>
       </c>
       <c r="V862" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
       <c r="W862" t="s">
-        <v>514</v>
+        <v>1465</v>
       </c>
       <c r="X862" t="s">
         <v>527</v>
@@ -23799,10 +23847,10 @@
         <v>93</v>
       </c>
       <c r="V863" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="W863" t="s">
-        <v>514</v>
+        <v>1465</v>
       </c>
       <c r="X863" t="s">
         <v>527</v>
@@ -23813,10 +23861,10 @@
         <v>93</v>
       </c>
       <c r="V864" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="W864" t="s">
-        <v>1182</v>
+        <v>495</v>
       </c>
       <c r="X864" t="s">
         <v>527</v>
@@ -23827,10 +23875,10 @@
         <v>93</v>
       </c>
       <c r="V865" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="W865" t="s">
-        <v>1182</v>
+        <v>495</v>
       </c>
       <c r="X865" t="s">
         <v>527</v>
@@ -23841,10 +23889,10 @@
         <v>93</v>
       </c>
       <c r="V866" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="W866" t="s">
-        <v>1186</v>
+        <v>1152</v>
       </c>
       <c r="X866" t="s">
         <v>527</v>
@@ -23855,10 +23903,10 @@
         <v>93</v>
       </c>
       <c r="V867" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="W867" t="s">
-        <v>1186</v>
+        <v>1152</v>
       </c>
       <c r="X867" t="s">
         <v>527</v>
@@ -23869,10 +23917,10 @@
         <v>93</v>
       </c>
       <c r="V868" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="W868" t="s">
-        <v>1190</v>
+        <v>1156</v>
       </c>
       <c r="X868" t="s">
         <v>527</v>
@@ -23883,10 +23931,10 @@
         <v>93</v>
       </c>
       <c r="V869" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="W869" t="s">
-        <v>1190</v>
+        <v>1156</v>
       </c>
       <c r="X869" t="s">
         <v>527</v>
@@ -23897,10 +23945,10 @@
         <v>93</v>
       </c>
       <c r="V870" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="W870" t="s">
-        <v>1194</v>
+        <v>1160</v>
       </c>
       <c r="X870" t="s">
         <v>527</v>
@@ -23911,10 +23959,10 @@
         <v>93</v>
       </c>
       <c r="V871" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="W871" t="s">
-        <v>1194</v>
+        <v>1160</v>
       </c>
       <c r="X871" t="s">
         <v>527</v>
@@ -23925,10 +23973,10 @@
         <v>93</v>
       </c>
       <c r="V872" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="W872" t="s">
-        <v>1198</v>
+        <v>1164</v>
       </c>
       <c r="X872" t="s">
         <v>527</v>
@@ -23939,10 +23987,10 @@
         <v>93</v>
       </c>
       <c r="V873" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="W873" t="s">
-        <v>1198</v>
+        <v>1164</v>
       </c>
       <c r="X873" t="s">
         <v>527</v>
@@ -23953,10 +24001,10 @@
         <v>93</v>
       </c>
       <c r="V874" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="W874" t="s">
-        <v>1202</v>
+        <v>1168</v>
       </c>
       <c r="X874" t="s">
         <v>527</v>
@@ -23967,10 +24015,10 @@
         <v>93</v>
       </c>
       <c r="V875" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="W875" t="s">
-        <v>1202</v>
+        <v>1168</v>
       </c>
       <c r="X875" t="s">
         <v>527</v>
@@ -23981,10 +24029,10 @@
         <v>93</v>
       </c>
       <c r="V876" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="W876" t="s">
-        <v>1206</v>
+        <v>1172</v>
       </c>
       <c r="X876" t="s">
         <v>527</v>
@@ -23995,10 +24043,10 @@
         <v>93</v>
       </c>
       <c r="V877" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="W877" t="s">
-        <v>1206</v>
+        <v>1172</v>
       </c>
       <c r="X877" t="s">
         <v>527</v>
@@ -24009,10 +24057,10 @@
         <v>93</v>
       </c>
       <c r="V878" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="W878" t="s">
-        <v>1210</v>
+        <v>1182</v>
       </c>
       <c r="X878" t="s">
         <v>527</v>
@@ -24023,10 +24071,10 @@
         <v>93</v>
       </c>
       <c r="V879" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="W879" t="s">
-        <v>1210</v>
+        <v>1182</v>
       </c>
       <c r="X879" t="s">
         <v>527</v>
@@ -24037,10 +24085,10 @@
         <v>93</v>
       </c>
       <c r="V880" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="W880" t="s">
-        <v>1217</v>
+        <v>1186</v>
       </c>
       <c r="X880" t="s">
         <v>527</v>
@@ -24051,10 +24099,10 @@
         <v>93</v>
       </c>
       <c r="V881" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="W881" t="s">
-        <v>1217</v>
+        <v>1186</v>
       </c>
       <c r="X881" t="s">
         <v>527</v>
@@ -24065,10 +24113,10 @@
         <v>93</v>
       </c>
       <c r="V882" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="W882" t="s">
-        <v>496</v>
+        <v>1190</v>
       </c>
       <c r="X882" t="s">
         <v>527</v>
@@ -24079,10 +24127,10 @@
         <v>93</v>
       </c>
       <c r="V883" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="W883" t="s">
-        <v>496</v>
+        <v>1190</v>
       </c>
       <c r="X883" t="s">
         <v>527</v>
@@ -24093,10 +24141,10 @@
         <v>93</v>
       </c>
       <c r="V884" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="W884" t="s">
-        <v>1224</v>
+        <v>1194</v>
       </c>
       <c r="X884" t="s">
         <v>527</v>
@@ -24107,10 +24155,10 @@
         <v>93</v>
       </c>
       <c r="V885" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="W885" t="s">
-        <v>1224</v>
+        <v>1194</v>
       </c>
       <c r="X885" t="s">
         <v>527</v>
@@ -24121,10 +24169,10 @@
         <v>93</v>
       </c>
       <c r="V886" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="W886" t="s">
-        <v>1228</v>
+        <v>1198</v>
       </c>
       <c r="X886" t="s">
         <v>527</v>
@@ -24135,10 +24183,10 @@
         <v>93</v>
       </c>
       <c r="V887" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="W887" t="s">
-        <v>1228</v>
+        <v>1198</v>
       </c>
       <c r="X887" t="s">
         <v>527</v>
@@ -24149,10 +24197,10 @@
         <v>93</v>
       </c>
       <c r="V888" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="W888" t="s">
-        <v>1235</v>
+        <v>1202</v>
       </c>
       <c r="X888" t="s">
         <v>527</v>
@@ -24163,10 +24211,10 @@
         <v>93</v>
       </c>
       <c r="V889" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="W889" t="s">
-        <v>1235</v>
+        <v>1202</v>
       </c>
       <c r="X889" t="s">
         <v>527</v>
@@ -24177,10 +24225,10 @@
         <v>93</v>
       </c>
       <c r="V890" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="W890" t="s">
-        <v>1239</v>
+        <v>1206</v>
       </c>
       <c r="X890" t="s">
         <v>527</v>
@@ -24191,10 +24239,10 @@
         <v>93</v>
       </c>
       <c r="V891" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="W891" t="s">
-        <v>1239</v>
+        <v>1206</v>
       </c>
       <c r="X891" t="s">
         <v>527</v>
@@ -24205,10 +24253,10 @@
         <v>93</v>
       </c>
       <c r="V892" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="W892" t="s">
-        <v>1246</v>
+        <v>1210</v>
       </c>
       <c r="X892" t="s">
         <v>527</v>
@@ -24219,10 +24267,10 @@
         <v>93</v>
       </c>
       <c r="V893" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="W893" t="s">
-        <v>1246</v>
+        <v>1210</v>
       </c>
       <c r="X893" t="s">
         <v>527</v>
@@ -24233,10 +24281,10 @@
         <v>93</v>
       </c>
       <c r="V894" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="W894" t="s">
-        <v>1253</v>
+        <v>496</v>
       </c>
       <c r="X894" t="s">
         <v>527</v>
@@ -24247,10 +24295,10 @@
         <v>93</v>
       </c>
       <c r="V895" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="W895" t="s">
-        <v>1253</v>
+        <v>496</v>
       </c>
       <c r="X895" t="s">
         <v>527</v>
@@ -24261,10 +24309,10 @@
         <v>93</v>
       </c>
       <c r="V896" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="W896" t="s">
-        <v>1257</v>
+        <v>1224</v>
       </c>
       <c r="X896" t="s">
         <v>527</v>
@@ -24275,10 +24323,10 @@
         <v>93</v>
       </c>
       <c r="V897" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="W897" t="s">
-        <v>1257</v>
+        <v>1224</v>
       </c>
       <c r="X897" t="s">
         <v>527</v>
@@ -24289,10 +24337,10 @@
         <v>93</v>
       </c>
       <c r="V898" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="W898" t="s">
-        <v>1261</v>
+        <v>1228</v>
       </c>
       <c r="X898" t="s">
         <v>527</v>
@@ -24303,10 +24351,10 @@
         <v>93</v>
       </c>
       <c r="V899" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="W899" t="s">
-        <v>1261</v>
+        <v>1228</v>
       </c>
       <c r="X899" t="s">
         <v>527</v>
@@ -24317,10 +24365,10 @@
         <v>93</v>
       </c>
       <c r="V900" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="W900" t="s">
-        <v>1265</v>
+        <v>1235</v>
       </c>
       <c r="X900" t="s">
         <v>527</v>
@@ -24331,10 +24379,10 @@
         <v>93</v>
       </c>
       <c r="V901" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="W901" t="s">
-        <v>1265</v>
+        <v>1235</v>
       </c>
       <c r="X901" t="s">
         <v>527</v>
@@ -24345,10 +24393,10 @@
         <v>93</v>
       </c>
       <c r="V902" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="W902" t="s">
-        <v>1269</v>
+        <v>1239</v>
       </c>
       <c r="X902" t="s">
         <v>527</v>
@@ -24359,10 +24407,10 @@
         <v>93</v>
       </c>
       <c r="V903" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="W903" t="s">
-        <v>1269</v>
+        <v>1239</v>
       </c>
       <c r="X903" t="s">
         <v>527</v>
@@ -24373,10 +24421,10 @@
         <v>93</v>
       </c>
       <c r="V904" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="W904" t="s">
-        <v>1273</v>
+        <v>1246</v>
       </c>
       <c r="X904" t="s">
         <v>527</v>
@@ -24387,10 +24435,10 @@
         <v>93</v>
       </c>
       <c r="V905" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="W905" t="s">
-        <v>1273</v>
+        <v>1246</v>
       </c>
       <c r="X905" t="s">
         <v>527</v>
@@ -24401,10 +24449,10 @@
         <v>93</v>
       </c>
       <c r="V906" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="W906" t="s">
-        <v>1280</v>
+        <v>1253</v>
       </c>
       <c r="X906" t="s">
         <v>527</v>
@@ -24415,10 +24463,10 @@
         <v>93</v>
       </c>
       <c r="V907" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="W907" t="s">
-        <v>1280</v>
+        <v>1253</v>
       </c>
       <c r="X907" t="s">
         <v>527</v>
@@ -24429,10 +24477,10 @@
         <v>93</v>
       </c>
       <c r="V908" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="W908" t="s">
-        <v>1284</v>
+        <v>1257</v>
       </c>
       <c r="X908" t="s">
         <v>527</v>
@@ -24443,10 +24491,10 @@
         <v>93</v>
       </c>
       <c r="V909" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="W909" t="s">
-        <v>1284</v>
+        <v>1257</v>
       </c>
       <c r="X909" t="s">
         <v>527</v>
@@ -24457,10 +24505,10 @@
         <v>93</v>
       </c>
       <c r="V910" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="W910" t="s">
-        <v>1288</v>
+        <v>1261</v>
       </c>
       <c r="X910" t="s">
         <v>527</v>
@@ -24471,10 +24519,10 @@
         <v>93</v>
       </c>
       <c r="V911" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="W911" t="s">
-        <v>1288</v>
+        <v>1261</v>
       </c>
       <c r="X911" t="s">
         <v>527</v>
@@ -24485,10 +24533,10 @@
         <v>93</v>
       </c>
       <c r="V912" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="W912" t="s">
-        <v>510</v>
+        <v>1265</v>
       </c>
       <c r="X912" t="s">
         <v>527</v>
@@ -24499,10 +24547,10 @@
         <v>93</v>
       </c>
       <c r="V913" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="W913" t="s">
-        <v>510</v>
+        <v>1265</v>
       </c>
       <c r="X913" t="s">
         <v>527</v>
@@ -24513,10 +24561,10 @@
         <v>93</v>
       </c>
       <c r="V914" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="W914" t="s">
-        <v>1295</v>
+        <v>1269</v>
       </c>
       <c r="X914" t="s">
         <v>527</v>
@@ -24527,10 +24575,10 @@
         <v>93</v>
       </c>
       <c r="V915" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="W915" t="s">
-        <v>1295</v>
+        <v>1269</v>
       </c>
       <c r="X915" t="s">
         <v>527</v>
@@ -24541,10 +24589,10 @@
         <v>93</v>
       </c>
       <c r="V916" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="W916" t="s">
-        <v>517</v>
+        <v>1273</v>
       </c>
       <c r="X916" t="s">
         <v>527</v>
@@ -24555,10 +24603,10 @@
         <v>93</v>
       </c>
       <c r="V917" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="W917" t="s">
-        <v>517</v>
+        <v>1273</v>
       </c>
       <c r="X917" t="s">
         <v>527</v>
@@ -24569,10 +24617,10 @@
         <v>93</v>
       </c>
       <c r="V918" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="W918" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="X918" t="s">
         <v>527</v>
@@ -24583,10 +24631,10 @@
         <v>93</v>
       </c>
       <c r="V919" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="W919" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="X919" t="s">
         <v>527</v>
@@ -24597,10 +24645,10 @@
         <v>93</v>
       </c>
       <c r="V920" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="W920" t="s">
-        <v>1306</v>
+        <v>1284</v>
       </c>
       <c r="X920" t="s">
         <v>527</v>
@@ -24611,10 +24659,10 @@
         <v>93</v>
       </c>
       <c r="V921" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="W921" t="s">
-        <v>1306</v>
+        <v>1284</v>
       </c>
       <c r="X921" t="s">
         <v>527</v>
@@ -24625,10 +24673,10 @@
         <v>93</v>
       </c>
       <c r="V922" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="W922" t="s">
-        <v>1310</v>
+        <v>1288</v>
       </c>
       <c r="X922" t="s">
         <v>527</v>
@@ -24639,10 +24687,10 @@
         <v>93</v>
       </c>
       <c r="V923" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="W923" t="s">
-        <v>1310</v>
+        <v>1288</v>
       </c>
       <c r="X923" t="s">
         <v>527</v>
@@ -24653,10 +24701,10 @@
         <v>93</v>
       </c>
       <c r="V924" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="W924" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="X924" t="s">
         <v>527</v>
@@ -24667,10 +24715,10 @@
         <v>93</v>
       </c>
       <c r="V925" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="W925" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="X925" t="s">
         <v>527</v>
@@ -24681,10 +24729,10 @@
         <v>93</v>
       </c>
       <c r="V926" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="W926" t="s">
-        <v>1317</v>
+        <v>1295</v>
       </c>
       <c r="X926" t="s">
         <v>527</v>
@@ -24695,12 +24743,180 @@
         <v>93</v>
       </c>
       <c r="V927" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="W927" t="s">
+        <v>1295</v>
+      </c>
+      <c r="X927" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="928" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U928" t="s">
+        <v>93</v>
+      </c>
+      <c r="V928" t="s">
+        <v>1531</v>
+      </c>
+      <c r="W928" t="s">
+        <v>517</v>
+      </c>
+      <c r="X928" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="929" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U929" t="s">
+        <v>93</v>
+      </c>
+      <c r="V929" t="s">
+        <v>1532</v>
+      </c>
+      <c r="W929" t="s">
+        <v>517</v>
+      </c>
+      <c r="X929" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="930" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U930" t="s">
+        <v>93</v>
+      </c>
+      <c r="V930" t="s">
+        <v>1533</v>
+      </c>
+      <c r="W930" t="s">
+        <v>1302</v>
+      </c>
+      <c r="X930" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="931" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U931" t="s">
+        <v>93</v>
+      </c>
+      <c r="V931" t="s">
+        <v>1534</v>
+      </c>
+      <c r="W931" t="s">
+        <v>1302</v>
+      </c>
+      <c r="X931" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="932" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U932" t="s">
+        <v>93</v>
+      </c>
+      <c r="V932" t="s">
+        <v>1535</v>
+      </c>
+      <c r="W932" t="s">
+        <v>1306</v>
+      </c>
+      <c r="X932" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="933" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U933" t="s">
+        <v>93</v>
+      </c>
+      <c r="V933" t="s">
+        <v>1536</v>
+      </c>
+      <c r="W933" t="s">
+        <v>1306</v>
+      </c>
+      <c r="X933" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="934" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U934" t="s">
+        <v>93</v>
+      </c>
+      <c r="V934" t="s">
+        <v>1537</v>
+      </c>
+      <c r="W934" t="s">
+        <v>1310</v>
+      </c>
+      <c r="X934" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="935" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U935" t="s">
+        <v>93</v>
+      </c>
+      <c r="V935" t="s">
+        <v>1538</v>
+      </c>
+      <c r="W935" t="s">
+        <v>1310</v>
+      </c>
+      <c r="X935" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="936" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U936" t="s">
+        <v>93</v>
+      </c>
+      <c r="V936" t="s">
+        <v>1539</v>
+      </c>
+      <c r="W936" t="s">
+        <v>505</v>
+      </c>
+      <c r="X936" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="937" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U937" t="s">
+        <v>93</v>
+      </c>
+      <c r="V937" t="s">
+        <v>1540</v>
+      </c>
+      <c r="W937" t="s">
+        <v>505</v>
+      </c>
+      <c r="X937" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="938" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U938" t="s">
+        <v>93</v>
+      </c>
+      <c r="V938" t="s">
+        <v>1541</v>
+      </c>
+      <c r="W938" t="s">
         <v>1317</v>
       </c>
-      <c r="X927" t="s">
+      <c r="X938" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="939" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U939" t="s">
+        <v>93</v>
+      </c>
+      <c r="V939" t="s">
+        <v>1542</v>
+      </c>
+      <c r="W939" t="s">
+        <v>1317</v>
+      </c>
+      <c r="X939" t="s">
         <v>527</v>
       </c>
     </row>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25EA0612-4337-4389-A895-FF34B9C1894B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25D07362-BE47-4865-9693-52F94BD486B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12DCFD3-F3B3-4479-99A4-A4BD0525DE36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB560E7A-9517-4DAC-93FA-B519AB56377B}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25D07362-BE47-4865-9693-52F94BD486B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFD277B7-5068-4E0D-865F-34DFD9FFFC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB560E7A-9517-4DAC-93FA-B519AB56377B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{827F8126-E2C5-4730-919A-8B34FF03ECB0}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFD277B7-5068-4E0D-865F-34DFD9FFFC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D239127-1D60-4EFA-8789-5C793892E094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{827F8126-E2C5-4730-919A-8B34FF03ECB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944D6870-8CC5-4CE8-BAB8-504C8186F324}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D239127-1D60-4EFA-8789-5C793892E094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9451AA3-E056-4A5C-9DC0-64D8888D38C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944D6870-8CC5-4CE8-BAB8-504C8186F324}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5A9177F-B42C-44F2-9D50-1AE17AA0F5E4}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9451AA3-E056-4A5C-9DC0-64D8888D38C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{052C8598-6AD3-434A-930C-EDC2E4851610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5A9177F-B42C-44F2-9D50-1AE17AA0F5E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35AEC848-8255-4408-8164-61F98C3C9BB8}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{052C8598-6AD3-434A-930C-EDC2E4851610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB829F1C-B9C1-4EC0-BD23-A7D77A66C06F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35AEC848-8255-4408-8164-61F98C3C9BB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04FF97FB-8825-43ED-8DDC-3EDDD20E2462}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB829F1C-B9C1-4EC0-BD23-A7D77A66C06F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{320D1D0E-69A6-4C38-B83B-6C673679961E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04FF97FB-8825-43ED-8DDC-3EDDD20E2462}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBA318E-1F3D-4857-8A55-B5D59234C93B}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{320D1D0E-69A6-4C38-B83B-6C673679961E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8A4AE7A-0A91-400D-B8FD-8116318B82C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBA318E-1F3D-4857-8A55-B5D59234C93B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACD1913-B53D-41BD-9B1C-B0436D868E53}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8A4AE7A-0A91-400D-B8FD-8116318B82C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E731AD62-BC25-4E56-81CC-CA455667C930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACD1913-B53D-41BD-9B1C-B0436D868E53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6B007C-CA14-4C98-8D68-ECD23AD8F989}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E731AD62-BC25-4E56-81CC-CA455667C930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8413654B-26E9-41EA-885F-5194E9ABA598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6B007C-CA14-4C98-8D68-ECD23AD8F989}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36E42160-A48C-4C3C-ADB3-A083B0B29544}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8413654B-26E9-41EA-885F-5194E9ABA598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FA5E078-A1F9-4E09-8071-E1FAC91C2954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36E42160-A48C-4C3C-ADB3-A083B0B29544}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FE21D78-6789-4ED3-8F9E-D79DD36DF65D}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FA5E078-A1F9-4E09-8071-E1FAC91C2954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA3D2A71-6A2F-43A4-8A14-A2F897663B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FE21D78-6789-4ED3-8F9E-D79DD36DF65D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78729D01-3F6C-42AB-B3F2-C2A327197BC8}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA3D2A71-6A2F-43A4-8A14-A2F897663B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC13060F-D81F-4A1B-A35F-C1EC467F9717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78729D01-3F6C-42AB-B3F2-C2A327197BC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E47AB4C9-0B11-445E-81DA-D47DC30F1609}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC13060F-D81F-4A1B-A35F-C1EC467F9717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC8B05D0-F5E8-4022-A60A-72FDE2FE07D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5259,7 +5259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E47AB4C9-0B11-445E-81DA-D47DC30F1609}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D60A063-19D0-488F-9F32-5D8534CFD699}">
   <dimension ref="B2:AE939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC8B05D0-F5E8-4022-A60A-72FDE2FE07D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACBDF5B-5BCE-464C-9897-9627C6C7AD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6503" uniqueCount="1550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6510" uniqueCount="1552">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -4773,7 +4773,13 @@
     <t>pset_set</t>
   </si>
   <si>
-    <t>ELE,DMD,PRE</t>
+    <t>STGOUT_BND</t>
+  </si>
+  <si>
+    <t>DMD,PRE,ELE</t>
+  </si>
+  <si>
+    <t>STG</t>
   </si>
 </sst>
 </file>
@@ -4909,7 +4915,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4922,6 +4928,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -5260,10 +5267,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D60A063-19D0-488F-9F32-5D8534CFD699}">
-  <dimension ref="B2:AE939"/>
+  <dimension ref="B2:AG939"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -5277,7 +5284,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="3" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -5326,11 +5333,17 @@
       <c r="X3" t="s">
         <v>482</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" s="12" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="4" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="AB3" s="12"/>
+      <c r="AC3" s="12"/>
+      <c r="AD3" s="12"/>
+      <c r="AE3" s="12"/>
+      <c r="AF3" s="12"/>
+      <c r="AG3" s="12"/>
+    </row>
+    <row r="4" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>97</v>
       </c>
@@ -5379,23 +5392,29 @@
       <c r="X4" t="s">
         <v>527</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AA4" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AB4" s="12" t="s">
         <v>1544</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" s="12" t="s">
         <v>1546</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AD4" s="12" t="s">
         <v>1547</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AE4" s="12" t="s">
+        <v>1549</v>
+      </c>
+      <c r="AF4" s="12" t="s">
         <v>1548</v>
       </c>
-    </row>
-    <row r="5" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="AG4" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>98</v>
       </c>
@@ -5444,23 +5463,27 @@
       <c r="X5" t="s">
         <v>527</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AA5" s="12" t="s">
         <v>1543</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AB5" s="12" t="s">
         <v>1545</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="12">
         <v>2</v>
       </c>
-      <c r="AD5">
+      <c r="AD5" s="12">
         <v>0</v>
       </c>
-      <c r="AE5" t="s">
-        <v>1549</v>
-      </c>
-    </row>
-    <row r="6" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="AE5" s="12"/>
+      <c r="AF5" s="12" t="s">
+        <v>1550</v>
+      </c>
+      <c r="AG5" s="12" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="6" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>99</v>
       </c>
@@ -5509,8 +5532,27 @@
       <c r="X6" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="7" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="AA6" s="12" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AB6" s="12" t="s">
+        <v>1545</v>
+      </c>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="12">
+        <v>2</v>
+      </c>
+      <c r="AF6" s="12" t="s">
+        <v>1551</v>
+      </c>
+      <c r="AG6" s="12" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>100</v>
       </c>
@@ -5560,7 +5602,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="8" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>101</v>
       </c>
@@ -5610,7 +5652,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="9" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>102</v>
       </c>
@@ -5660,7 +5702,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="10" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>103</v>
       </c>
@@ -5710,7 +5752,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="11" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>104</v>
       </c>
@@ -5760,7 +5802,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="12" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>105</v>
       </c>
@@ -5810,7 +5852,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="13" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>106</v>
       </c>
@@ -5860,7 +5902,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="14" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>107</v>
       </c>
@@ -5910,7 +5952,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="15" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>108</v>
       </c>
@@ -5960,7 +6002,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="16" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>109</v>
       </c>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACBDF5B-5BCE-464C-9897-9627C6C7AD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C6C6B2-5CEC-436E-85D4-2640EA42B4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -4915,7 +4915,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4928,7 +4928,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -5333,15 +5332,9 @@
       <c r="X3" t="s">
         <v>482</v>
       </c>
-      <c r="AA3" s="12" t="s">
+      <c r="AA3" t="s">
         <v>315</v>
       </c>
-      <c r="AB3" s="12"/>
-      <c r="AC3" s="12"/>
-      <c r="AD3" s="12"/>
-      <c r="AE3" s="12"/>
-      <c r="AF3" s="12"/>
-      <c r="AG3" s="12"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
@@ -5392,25 +5385,25 @@
       <c r="X4" t="s">
         <v>527</v>
       </c>
-      <c r="AA4" s="12" t="s">
+      <c r="AA4" t="s">
         <v>316</v>
       </c>
-      <c r="AB4" s="12" t="s">
+      <c r="AB4" t="s">
         <v>1544</v>
       </c>
-      <c r="AC4" s="12" t="s">
+      <c r="AC4" t="s">
         <v>1546</v>
       </c>
-      <c r="AD4" s="12" t="s">
+      <c r="AD4" t="s">
         <v>1547</v>
       </c>
-      <c r="AE4" s="12" t="s">
+      <c r="AE4" t="s">
         <v>1549</v>
       </c>
-      <c r="AF4" s="12" t="s">
+      <c r="AF4" t="s">
         <v>1548</v>
       </c>
-      <c r="AG4" s="12" t="s">
+      <c r="AG4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -5463,23 +5456,22 @@
       <c r="X5" t="s">
         <v>527</v>
       </c>
-      <c r="AA5" s="12" t="s">
+      <c r="AA5" t="s">
         <v>1543</v>
       </c>
-      <c r="AB5" s="12" t="s">
+      <c r="AB5" t="s">
         <v>1545</v>
       </c>
-      <c r="AC5" s="12">
+      <c r="AC5">
         <v>2</v>
       </c>
-      <c r="AD5" s="12">
+      <c r="AD5">
         <v>0</v>
       </c>
-      <c r="AE5" s="12"/>
-      <c r="AF5" s="12" t="s">
+      <c r="AF5" t="s">
         <v>1550</v>
       </c>
-      <c r="AG5" s="12" t="s">
+      <c r="AG5" t="s">
         <v>1543</v>
       </c>
     </row>
@@ -5532,23 +5524,22 @@
       <c r="X6" t="s">
         <v>527</v>
       </c>
-      <c r="AA6" s="12" t="s">
+      <c r="AA6" t="s">
         <v>1543</v>
       </c>
-      <c r="AB6" s="12" t="s">
+      <c r="AB6" t="s">
         <v>1545</v>
       </c>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="12">
+      <c r="AD6">
         <v>0</v>
       </c>
-      <c r="AE6" s="12">
+      <c r="AE6">
         <v>2</v>
       </c>
-      <c r="AF6" s="12" t="s">
+      <c r="AF6" t="s">
         <v>1551</v>
       </c>
-      <c r="AG6" s="12" t="s">
+      <c r="AG6" t="s">
         <v>1543</v>
       </c>
     </row>
@@ -25474,8 +25465,8 @@
         <v>1</v>
       </c>
       <c r="AB15">
-        <f>AE15*2.5</f>
-        <v>82.699999999999989</v>
+        <f>AE15*1.1</f>
+        <v>36.387999999999998</v>
       </c>
       <c r="AC15">
         <v>3</v>
